--- a/artfynd/A 39825-2020 artfynd.xlsx
+++ b/artfynd/A 39825-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122555335</v>
       </c>
       <c r="B2" t="n">
-        <v>57324</v>
+        <v>57325</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 39825-2020 artfynd.xlsx
+++ b/artfynd/A 39825-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,118 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123265125</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Jungfruboda, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>474478</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6596685</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39825-2020 artfynd.xlsx
+++ b/artfynd/A 39825-2020 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>123265125</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 39825-2020 artfynd.xlsx
+++ b/artfynd/A 39825-2020 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>123265125</v>
       </c>
       <c r="B3" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 39825-2020 artfynd.xlsx
+++ b/artfynd/A 39825-2020 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>123265125</v>
       </c>
       <c r="B3" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 39825-2020 artfynd.xlsx
+++ b/artfynd/A 39825-2020 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>123265125</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 39825-2020 artfynd.xlsx
+++ b/artfynd/A 39825-2020 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>123265125</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 39825-2020 artfynd.xlsx
+++ b/artfynd/A 39825-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,7 +792,7 @@
         <v>123265125</v>
       </c>
       <c r="B3" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -898,6 +898,240 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123929005</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90955</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Jungfruboda, Jungfruboda, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>474487</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6596794</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123928720</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57382</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Jungfruboda, Jungfruboda, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>474533</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6596834</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Risbo där de tidigare häckat.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39825-2020 artfynd.xlsx
+++ b/artfynd/A 39825-2020 artfynd.xlsx
@@ -901,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123929005</v>
+        <v>123929040</v>
       </c>
       <c r="B4" t="n">
         <v>90955</v>

--- a/artfynd/A 39825-2020 artfynd.xlsx
+++ b/artfynd/A 39825-2020 artfynd.xlsx
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123929040</v>
+        <v>123928720</v>
       </c>
       <c r="B4" t="n">
-        <v>90955</v>
+        <v>57382</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,41 +913,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Jungfruboda, Jungfruboda, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474487</v>
+        <v>474533</v>
       </c>
       <c r="R4" t="n">
-        <v>6596794</v>
+        <v>6596834</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +991,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Risbo där de tidigare häckat.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123928720</v>
+        <v>123929040</v>
       </c>
       <c r="B5" t="n">
-        <v>57382</v>
+        <v>90955</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,46 +1035,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100001</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Jungfruboda, Jungfruboda, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474533</v>
+        <v>474487</v>
       </c>
       <c r="R5" t="n">
-        <v>6596834</v>
+        <v>6596794</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,12 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Risbo där de tidigare häckat.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 39825-2020 artfynd.xlsx
+++ b/artfynd/A 39825-2020 artfynd.xlsx
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123928720</v>
+        <v>123929005</v>
       </c>
       <c r="B4" t="n">
-        <v>57382</v>
+        <v>90955</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,46 +913,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100001</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Jungfruboda, Jungfruboda, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474533</v>
+        <v>474487</v>
       </c>
       <c r="R4" t="n">
-        <v>6596834</v>
+        <v>6596794</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,12 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Risbo där de tidigare häckat.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123929040</v>
+        <v>123928720</v>
       </c>
       <c r="B5" t="n">
-        <v>90955</v>
+        <v>57382</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,41 +1025,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Jungfruboda, Jungfruboda, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474487</v>
+        <v>474533</v>
       </c>
       <c r="R5" t="n">
-        <v>6596794</v>
+        <v>6596834</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1103,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Risbo där de tidigare häckat.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 39825-2020 artfynd.xlsx
+++ b/artfynd/A 39825-2020 artfynd.xlsx
@@ -901,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123929040</v>
+        <v>123929005</v>
       </c>
       <c r="B4" t="n">
         <v>90977</v>

--- a/artfynd/A 39825-2020 artfynd.xlsx
+++ b/artfynd/A 39825-2020 artfynd.xlsx
@@ -901,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123929005</v>
+        <v>123929040</v>
       </c>
       <c r="B4" t="n">
         <v>90977</v>

--- a/artfynd/A 39825-2020 artfynd.xlsx
+++ b/artfynd/A 39825-2020 artfynd.xlsx
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123929040</v>
+        <v>123928720</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>57404</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,41 +913,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Jungfruboda, Jungfruboda, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474487</v>
+        <v>474533</v>
       </c>
       <c r="R4" t="n">
-        <v>6596794</v>
+        <v>6596834</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +991,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Risbo där de tidigare häckat.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123928720</v>
+        <v>123929040</v>
       </c>
       <c r="B5" t="n">
-        <v>57404</v>
+        <v>90977</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,46 +1035,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100001</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Jungfruboda, Jungfruboda, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474533</v>
+        <v>474487</v>
       </c>
       <c r="R5" t="n">
-        <v>6596834</v>
+        <v>6596794</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,12 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Risbo där de tidigare häckat.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
